--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/06,10,26 Останкино СЫРЫ/дв 06,10,26 мррсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/06,10,26 Останкино СЫРЫ/дв 06,10,26 мррсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\06,10,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB88C1B0-E423-4C9E-9EAD-739E0D405531}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C758B7F8-2AA7-4060-BC8E-F74D36116F21}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,7 +328,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,6 +348,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -387,7 +393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -400,6 +406,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2675,7 +2682,7 @@
       </c>
       <c r="T5" s="4">
         <f t="shared" si="1"/>
-        <v>1860</v>
+        <v>1836</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="1"/>
@@ -3122,9 +3129,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="T10" s="5">
-        <f>VLOOKUP(A10,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T10" s="12">
+        <v>0</v>
       </c>
       <c r="U10" s="11"/>
       <c r="V10" s="1" t="e">
@@ -3217,9 +3223,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="T11" s="5">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T11" s="12">
+        <v>0</v>
       </c>
       <c r="U11" s="11"/>
       <c r="V11" s="1" t="e">
